--- a/renewables_comps.xlsx
+++ b/renewables_comps.xlsx
@@ -530,7 +530,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of April 23, 2026</t>
+          <t>As of April 28, 2026</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>4700.074496</v>
+        <v>4520.188928</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>1243.78304</v>
@@ -645,16 +645,16 @@
         <v>131.783945</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>4431.00352</v>
+        <v>4251.117952</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>3.008179744075595</v>
+        <v>2.886056590829006</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>18.54744713659456</v>
+        <v>17.79447593084921</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>27.30490210731944</v>
+        <v>26.2598638150669</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>20865.325056</v>
+        <v>21045.305344</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>655.334976</v>
@@ -685,16 +685,16 @@
         <v>107.45076</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>18665.29696</v>
+        <v>18845.277248</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>3.576154793648165</v>
+        <v>3.610637897296219</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>8.779207254665865</v>
+        <v>8.863860836845275</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>13.65327131288974</v>
+        <v>13.77104180994362</v>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>3035.74528</v>
+        <v>3054.586112</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>14846.324736</v>
@@ -725,16 +725,16 @@
         <v>235.511653</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>17048.889984</v>
+        <v>17067.730816</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>5.765609262412809</v>
+        <v>5.771980872270853</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>28.44093375986546</v>
+        <v>28.47236400872011</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>6.781606097702639</v>
+        <v>6.823694971897312</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -751,37 +751,37 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>201127.460864</v>
+        <v>201256.30464</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>97220.001792</v>
+        <v>104403.001344</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>2812</v>
+        <v>1998</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>27412.000768</v>
+        <v>27865.99936</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>14138.000384</v>
+        <v>14158.999552</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>6834.999808</v>
+        <v>8184</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>2085.302855</v>
+        <v>2085.341456</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>295535.462656</v>
+        <v>303661.305984</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>10.78124377557292</v>
+        <v>10.89719776638938</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>20.90362530973319</v>
+        <v>21.44652274821966</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>29.42611068234283</v>
+        <v>24.59143507331378</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>10314.8544</v>
+        <v>10167.980032</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>36546.998272</v>
@@ -812,16 +812,16 @@
         <v>305.987962</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>44269.852672</v>
+        <v>44122.978304</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>6.909607028216818</v>
+        <v>6.886682981622021</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>13.49279290933823</v>
+        <v>13.44802778563663</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>187.5428072727273</v>
+        <v>184.8723642181818</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>4804.1216</v>
+        <v>4888.149504</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>9443.000319999999</v>
@@ -852,16 +852,16 @@
         <v>86.290173</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>13997.12192</v>
+        <v>14081.149824</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>9.795047268637527</v>
+        <v>9.853849163503391</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>13.3943750430622</v>
+        <v>13.47478452057416</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>28.4267550295858</v>
+        <v>28.92396156213018</v>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>10328.84224</v>
+        <v>10325.276672</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>30943.000576</v>
@@ -892,16 +892,16 @@
         <v>713.071623</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>39715.842816</v>
+        <v>39712.277248</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>3.246615141321292</v>
+        <v>3.246323670053521</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>11.42901930490439</v>
+        <v>11.42799324218948</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>10.9998319914803</v>
+        <v>10.99603479446219</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>40301.600768</v>
+        <v>40386.338816</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>28379.000832</v>
@@ -939,16 +939,16 @@
         <v>368.421246</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>67051.601664</v>
+        <v>67136.339712</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>3.963329187014919</v>
+        <v>3.968337938044791</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>11.13444042490728</v>
+        <v>11.14851183742785</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>19.92170019427147</v>
+        <v>19.96358751276836</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>4342.170112</v>
+        <v>4223.68384</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>997.171968</v>
@@ -986,10 +986,10 @@
         <v>1393.955129</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>4960.60208</v>
+        <v>4842.115808</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>6.987560901597875</v>
+        <v>6.820659781884743</v>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>67522.31424000001</v>
+        <v>64334.52032</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>2995.800064</v>
@@ -1030,13 +1030,13 @@
         <v>284.200747</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>68064.0064</v>
+        <v>64876.21248</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>33.62856161532939</v>
+        <v>32.05355993785405</v>
       </c>
       <c r="K18" s="10" t="n">
-        <v>489.538830069051</v>
+        <v>466.611162589018</v>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
